--- a/FinGraph_Fraud_Alerts.xlsx
+++ b/FinGraph_Fraud_Alerts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>HIGH RISK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TARGET01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SMURFING</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>198000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>9900</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>HIGH RISK</t>
         </is>
